--- a/artfynd/A 31213-2023 artfynd.xlsx
+++ b/artfynd/A 31213-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31213-2023 artfynd.xlsx
+++ b/artfynd/A 31213-2023 artfynd.xlsx
@@ -809,12 +809,7 @@
         <v>63942916</v>
       </c>
       <c r="B3" t="n">
-        <v>104015</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106417</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -850,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>420388.8338614641</v>
+        <v>420389</v>
       </c>
       <c r="R3" t="n">
-        <v>6153351.342857419</v>
+        <v>6153351</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -883,19 +878,9 @@
           <t>1994-05-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1994-05-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 31213-2023 artfynd.xlsx
+++ b/artfynd/A 31213-2023 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>63942916</v>
       </c>
       <c r="B3" t="n">
-        <v>106417</v>
+        <v>106429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31213-2023 artfynd.xlsx
+++ b/artfynd/A 31213-2023 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>63942916</v>
       </c>
       <c r="B3" t="n">
-        <v>106429</v>
+        <v>106438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31213-2023 artfynd.xlsx
+++ b/artfynd/A 31213-2023 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>63942916</v>
       </c>
       <c r="B3" t="n">
-        <v>106438</v>
+        <v>106443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31213-2023 artfynd.xlsx
+++ b/artfynd/A 31213-2023 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>63942916</v>
       </c>
       <c r="B3" t="n">
-        <v>106443</v>
+        <v>106471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31213-2023 artfynd.xlsx
+++ b/artfynd/A 31213-2023 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>63942916</v>
       </c>
       <c r="B3" t="n">
-        <v>106471</v>
+        <v>106477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31213-2023 artfynd.xlsx
+++ b/artfynd/A 31213-2023 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>63942916</v>
       </c>
       <c r="B3" t="n">
-        <v>106477</v>
+        <v>106484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31213-2023 artfynd.xlsx
+++ b/artfynd/A 31213-2023 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>63942916</v>
       </c>
       <c r="B3" t="n">
-        <v>106484</v>
+        <v>106488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31213-2023 artfynd.xlsx
+++ b/artfynd/A 31213-2023 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>63942916</v>
       </c>
       <c r="B3" t="n">
-        <v>106488</v>
+        <v>106495</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31213-2023 artfynd.xlsx
+++ b/artfynd/A 31213-2023 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>63942916</v>
       </c>
       <c r="B3" t="n">
-        <v>106498</v>
+        <v>106503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31213-2023 artfynd.xlsx
+++ b/artfynd/A 31213-2023 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>63942916</v>
       </c>
       <c r="B3" t="n">
-        <v>106503</v>
+        <v>106511</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31213-2023 artfynd.xlsx
+++ b/artfynd/A 31213-2023 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>63942916</v>
       </c>
       <c r="B3" t="n">
-        <v>106511</v>
+        <v>106521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 31213-2023 artfynd.xlsx
+++ b/artfynd/A 31213-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>494644</v>
+        <v>63942916</v>
       </c>
       <c r="B2" t="n">
-        <v>104015</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,19 +704,23 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ebbarps gård, 600m O, Sk</t>
+          <t>600m O Ebbarps gård, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>420437.9744278319</v>
+        <v>420389</v>
       </c>
       <c r="R2" t="n">
-        <v>6153401.966505233</v>
+        <v>6153351</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,34 +742,19 @@
           <t>Sövestad</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>M-Ysd-0269</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
           <t>1994-05-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1994-05-20</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2D1d1445, 2D1d1646</t>
+          <t>Veronica montana/2D1d1445/Sövestad s:n/SLa/ /Sven Larsson,Ystad</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,6 +763,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,139 +772,23 @@
           <t>bokskog</t>
         </is>
       </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>SkFlora    218448</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Skåne Floraväktarna</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Skåne Floraväktarna</t>
+          <t>Via Stefan Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>63942916</v>
-      </c>
-      <c r="B3" t="n">
-        <v>106521</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>1654</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Skogsveronika</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Veronica montana</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>600m O Ebbarps gård, Sk</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>420389</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6153351</v>
-      </c>
-      <c r="S3" t="n">
-        <v>100</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Ystad</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Sövestad</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>1994-05-20</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>1994-05-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Veronica montana/2D1d1445/Sövestad s:n/SLa/ /Sven Larsson,Ystad</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>bokskog</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>SkFlora    218448</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Stefan Andersson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Via Stefan Andersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
         <is>
           <t>Skånes Flora (1989-2006)</t>
         </is>

--- a/artfynd/A 31213-2023 artfynd.xlsx
+++ b/artfynd/A 31213-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>63942916</v>
+        <v>494644</v>
       </c>
       <c r="B2" t="n">
-        <v>106521</v>
+        <v>107042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -704,23 +704,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>600m O Ebbarps gård, Sk</t>
+          <t>Ebbarps gård, 600 m öster, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>420389</v>
+        <v>420395</v>
       </c>
       <c r="R2" t="n">
-        <v>6153351</v>
+        <v>6153209</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -742,6 +738,11 @@
           <t>Sövestad</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>M-Ysd-0269</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
           <t>1994-05-20</t>
@@ -754,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Veronica montana/2D1d1445/Sövestad s:n/SLa/ /Sven Larsson,Ystad</t>
+          <t>2D1d1445, 2D1d1646</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,7 +764,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,27 +772,249 @@
           <t>bokskog</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>SkFlora    218448</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Skåne Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Via Skåne Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>63942916</v>
+      </c>
+      <c r="B3" t="n">
+        <v>107042</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1654</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skogsveronika</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Veronica montana</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>600m O Ebbarps gård, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>420389</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6153351</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ystad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sövestad</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1994-05-20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1994-05-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Veronica montana/2D1d1445/Sövestad s:n/SLa/ /Sven Larsson,Ystad</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>bokskog</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>SkFlora    218448</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Stefan Andersson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Via Stefan Andersson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134208946</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99960</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skärmstarr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carex remota</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ebbarp, 400 m ONO, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>420372</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6153506</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ystad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sövestad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tomas Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tomas Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31213-2023 artfynd.xlsx
+++ b/artfynd/A 31213-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/494644</t>
         </is>
       </c>
     </row>
@@ -909,6 +919,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63942916</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,8 +1030,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134208946</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>